--- a/data/parametrosMesuales.xlsx
+++ b/data/parametrosMesuales.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyecto_Ia\Version20\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyecto_Ia\rex-tools-hub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE85E75-D8F8-4738-9283-9568A3D012BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEB1B831-7378-4259-8DE9-999EA2AE2E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4C61D130-B55A-40EB-8581-4AF412B8D4BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$U$140</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -628,7 +631,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -648,6 +651,7 @@
     <xf numFmtId="1" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares [0]" xfId="1" builtinId="6"/>
@@ -9317,45 +9321,57 @@
       <c r="A118" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
+      <c r="B118" s="16">
+        <v>41057.199999999997</v>
+      </c>
+      <c r="C118" s="2">
+        <v>90</v>
+      </c>
       <c r="D118" s="1">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E118" s="2"/>
+        <v>3695148</v>
+      </c>
+      <c r="E118" s="2">
+        <v>135.19999999999999</v>
+      </c>
       <c r="F118" s="1">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5550933</v>
       </c>
       <c r="G118" s="2">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="H118" s="1">
         <f t="shared" si="16"/>
-        <v>1.4999999999999999E-2</v>
+        <v>1.78E-2</v>
       </c>
       <c r="I118" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>6.3000000000000007</v>
       </c>
       <c r="J118" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="K118" s="2"/>
+        <v>258660</v>
+      </c>
+      <c r="K118" s="2">
+        <v>553553</v>
+      </c>
       <c r="L118" s="3">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M118" s="2"/>
+        <v>219115</v>
+      </c>
+      <c r="M118" s="17">
+        <v>71721</v>
+      </c>
       <c r="N118" s="2">
         <v>30</v>
       </c>
-      <c r="O118" s="2"/>
+      <c r="O118" s="2">
+        <v>4.2</v>
+      </c>
       <c r="P118" s="1">
         <f t="shared" si="15"/>
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="Q118" s="4">
         <v>46295</v>
@@ -9363,13 +9379,15 @@
       <c r="R118" s="2">
         <v>0.1</v>
       </c>
-      <c r="S118" s="2"/>
+      <c r="S118" s="2">
+        <v>0.72</v>
+      </c>
       <c r="T118" s="2">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="U118" s="2">
         <f t="shared" ref="U118:U140" si="19">+S118+G118</f>
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -9387,12 +9405,10 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G119" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G119" s="2"/>
       <c r="H119" s="1">
         <f t="shared" si="16"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I119" s="1">
         <f t="shared" si="17"/>
@@ -9423,12 +9439,10 @@
         <v>0.1</v>
       </c>
       <c r="S119" s="2"/>
-      <c r="T119" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T119" s="2"/>
       <c r="U119" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -9446,12 +9460,10 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G120" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G120" s="2"/>
       <c r="H120" s="1">
         <f t="shared" si="16"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I120" s="1">
         <f t="shared" si="17"/>
@@ -9482,12 +9494,10 @@
         <v>0.1</v>
       </c>
       <c r="S120" s="2"/>
-      <c r="T120" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T120" s="2"/>
       <c r="U120" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -9505,12 +9515,10 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G121" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G121" s="2"/>
       <c r="H121" s="1">
         <f t="shared" si="16"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I121" s="1">
         <f t="shared" si="17"/>
@@ -9541,12 +9549,10 @@
         <v>0.1</v>
       </c>
       <c r="S121" s="2"/>
-      <c r="T121" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T121" s="2"/>
       <c r="U121" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
@@ -9564,12 +9570,10 @@
         <f t="shared" ref="F122:F133" si="21">ROUND(B122*E122,0)</f>
         <v>0</v>
       </c>
-      <c r="G122" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G122" s="2"/>
       <c r="H122" s="1">
         <f t="shared" ref="H122:H133" si="22">G122/100</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I122" s="1">
         <f t="shared" ref="I122:I133" si="23">+C122*0.07</f>
@@ -9600,12 +9604,10 @@
         <v>0.1</v>
       </c>
       <c r="S122" s="2"/>
-      <c r="T122" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T122" s="2"/>
       <c r="U122" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
@@ -9623,12 +9625,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G123" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G123" s="2"/>
       <c r="H123" s="1">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I123" s="1">
         <f t="shared" si="23"/>
@@ -9659,12 +9659,10 @@
         <v>0.1</v>
       </c>
       <c r="S123" s="2"/>
-      <c r="T123" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T123" s="2"/>
       <c r="U123" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
@@ -9682,12 +9680,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G124" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G124" s="2"/>
       <c r="H124" s="1">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I124" s="1">
         <f t="shared" si="23"/>
@@ -9718,12 +9714,10 @@
         <v>0.1</v>
       </c>
       <c r="S124" s="2"/>
-      <c r="T124" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T124" s="2"/>
       <c r="U124" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
@@ -9741,12 +9735,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G125" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G125" s="2"/>
       <c r="H125" s="1">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I125" s="1">
         <f t="shared" si="23"/>
@@ -9777,12 +9769,10 @@
         <v>0.1</v>
       </c>
       <c r="S125" s="2"/>
-      <c r="T125" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T125" s="2"/>
       <c r="U125" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -9800,12 +9790,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G126" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G126" s="2"/>
       <c r="H126" s="1">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I126" s="1">
         <f t="shared" si="23"/>
@@ -9836,12 +9824,10 @@
         <v>0.1</v>
       </c>
       <c r="S126" s="2"/>
-      <c r="T126" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T126" s="2"/>
       <c r="U126" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
@@ -9859,12 +9845,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G127" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G127" s="2"/>
       <c r="H127" s="1">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I127" s="1">
         <f t="shared" si="23"/>
@@ -9895,12 +9879,10 @@
         <v>0.1</v>
       </c>
       <c r="S127" s="2"/>
-      <c r="T127" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T127" s="2"/>
       <c r="U127" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
@@ -9918,12 +9900,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G128" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G128" s="2"/>
       <c r="H128" s="1">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I128" s="1">
         <f t="shared" si="23"/>
@@ -9954,12 +9934,10 @@
         <v>0.1</v>
       </c>
       <c r="S128" s="2"/>
-      <c r="T128" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T128" s="2"/>
       <c r="U128" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
@@ -9977,12 +9955,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G129" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G129" s="2"/>
       <c r="H129" s="1">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I129" s="1">
         <f t="shared" si="23"/>
@@ -10013,12 +9989,10 @@
         <v>0.25</v>
       </c>
       <c r="S129" s="2"/>
-      <c r="T129" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T129" s="2"/>
       <c r="U129" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -10036,12 +10010,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G130" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G130" s="2"/>
       <c r="H130" s="1">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I130" s="1">
         <f t="shared" si="23"/>
@@ -10072,12 +10044,10 @@
         <v>0.25</v>
       </c>
       <c r="S130" s="2"/>
-      <c r="T130" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T130" s="2"/>
       <c r="U130" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -10095,12 +10065,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G131" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G131" s="2"/>
       <c r="H131" s="1">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I131" s="1">
         <f t="shared" si="23"/>
@@ -10131,12 +10099,10 @@
         <v>0.25</v>
       </c>
       <c r="S131" s="2"/>
-      <c r="T131" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T131" s="2"/>
       <c r="U131" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -10154,12 +10120,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G132" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G132" s="2"/>
       <c r="H132" s="1">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I132" s="1">
         <f t="shared" si="23"/>
@@ -10190,12 +10154,10 @@
         <v>0.25</v>
       </c>
       <c r="S132" s="2"/>
-      <c r="T132" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T132" s="2"/>
       <c r="U132" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
@@ -10213,12 +10175,10 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G133" s="11">
-        <v>1.5</v>
-      </c>
+      <c r="G133" s="11"/>
       <c r="H133" s="13">
         <f t="shared" si="22"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I133" s="13">
         <f t="shared" si="23"/>
@@ -10249,12 +10209,10 @@
         <v>0.25</v>
       </c>
       <c r="S133" s="2"/>
-      <c r="T133" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T133" s="2"/>
       <c r="U133" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
@@ -10272,12 +10230,10 @@
         <f t="shared" ref="F134:F140" si="27">ROUND(B134*E134,0)</f>
         <v>0</v>
       </c>
-      <c r="G134" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G134" s="2"/>
       <c r="H134" s="13">
         <f t="shared" ref="H134:H140" si="28">G134/100</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I134" s="13">
         <f t="shared" ref="I134:I140" si="29">+C134*0.07</f>
@@ -10309,12 +10265,10 @@
         <v>0.25</v>
       </c>
       <c r="S134" s="2"/>
-      <c r="T134" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T134" s="2"/>
       <c r="U134" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
@@ -10332,12 +10286,10 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G135" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G135" s="2"/>
       <c r="H135" s="1">
         <f t="shared" si="28"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I135" s="1">
         <f t="shared" si="29"/>
@@ -10369,12 +10321,10 @@
         <v>0.25</v>
       </c>
       <c r="S135" s="2"/>
-      <c r="T135" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T135" s="2"/>
       <c r="U135" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -10392,12 +10342,10 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G136" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G136" s="2"/>
       <c r="H136" s="1">
         <f t="shared" si="28"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I136" s="1">
         <f t="shared" si="29"/>
@@ -10429,12 +10377,10 @@
         <v>0.25</v>
       </c>
       <c r="S136" s="2"/>
-      <c r="T136" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T136" s="2"/>
       <c r="U136" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
@@ -10452,12 +10398,10 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G137" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G137" s="2"/>
       <c r="H137" s="1">
         <f t="shared" si="28"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I137" s="1">
         <f t="shared" si="29"/>
@@ -10489,12 +10433,10 @@
         <v>0.25</v>
       </c>
       <c r="S137" s="2"/>
-      <c r="T137" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T137" s="2"/>
       <c r="U137" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -10512,12 +10454,10 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G138" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G138" s="2"/>
       <c r="H138" s="1">
         <f t="shared" si="28"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I138" s="1">
         <f t="shared" si="29"/>
@@ -10549,12 +10489,10 @@
         <v>0.25</v>
       </c>
       <c r="S138" s="2"/>
-      <c r="T138" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T138" s="2"/>
       <c r="U138" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
@@ -10572,12 +10510,10 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G139" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G139" s="2"/>
       <c r="H139" s="1">
         <f t="shared" si="28"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I139" s="1">
         <f t="shared" si="29"/>
@@ -10609,12 +10545,10 @@
         <v>0.25</v>
       </c>
       <c r="S139" s="2"/>
-      <c r="T139" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T139" s="2"/>
       <c r="U139" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
@@ -10632,12 +10566,10 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G140" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="G140" s="2"/>
       <c r="H140" s="1">
         <f t="shared" si="28"/>
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I140" s="1">
         <f t="shared" si="29"/>
@@ -10669,12 +10601,10 @@
         <v>0.25</v>
       </c>
       <c r="S140" s="2"/>
-      <c r="T140" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="T140" s="2"/>
       <c r="U140" s="2">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
